--- a/output/_temp/etapa_2_actualizacion_mensual/_interno/registros_turno_aplicado.xlsx
+++ b/output/_temp/etapa_2_actualizacion_mensual/_interno/registros_turno_aplicado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1047,16 +1047,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ADTR</t>
+          <t>MP-01A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ASUP</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Muestreo manual de agua superficial</t>
+          <t>Medición de niveles freáticos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ADTR</t>
+          <t>MP-01A</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ASUP</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Muestreo manual de agua superficial</t>
+          <t>Medición de niveles freáticos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CPZ-05A</t>
+          <t>MP-01B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CPZ-05A</t>
+          <t>MP-01B</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1137,22 +1137,22 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CPZ-05B</t>
+          <t>MP-01B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>ASUB</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1161,22 +1161,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Muestreo manual  de aguas subterráneas</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CPZ-05B</t>
+          <t>MP-01B</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>ASUB</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Muestreo manual  de aguas subterráneas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CPZ-06A</t>
+          <t>MP-01C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1200,7 +1200,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CPZ-06A</t>
+          <t>MP-01C</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1233,22 +1233,22 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CPZ-06B</t>
+          <t>MP-01C</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>ASUB</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1257,22 +1257,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Muestreo manual  de aguas subterráneas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CPZ-06B</t>
+          <t>MP-01C</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>ASUB</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Muestreo manual  de aguas subterráneas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1281,13 +1281,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MP-07A</t>
+          <t>MP-02A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1296,7 +1296,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MP-07A</t>
+          <t>MP-02A</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MP-07A</t>
+          <t>MP-02A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MP-07A</t>
+          <t>MP-02A</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1377,13 +1377,13 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MP-07B_C</t>
+          <t>MP-02B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MP-07B_C</t>
+          <t>MP-02B</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MP-07B_C</t>
+          <t>MP-02B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MP-07B_C</t>
+          <t>MP-02B</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MP-07C</t>
+          <t>MP-02C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MP-07C</t>
+          <t>MP-02C</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1521,13 +1521,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MP-07C</t>
+          <t>MP-02C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MP-07C</t>
+          <t>MP-02C</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MP-08A</t>
+          <t>MP-03A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MP-08A</t>
+          <t>MP-03A</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1617,13 +1617,13 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MP-08A</t>
+          <t>MP-03A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MP-08A</t>
+          <t>MP-03A</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MP-08B_B</t>
+          <t>MP-03B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MP-08B_B</t>
+          <t>MP-03B</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MP-08B_B</t>
+          <t>MP-03B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MP-08B_B</t>
+          <t>MP-03B</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1761,13 +1761,13 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MP-08C</t>
+          <t>MP-03C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MP-08C</t>
+          <t>MP-03C</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MP-08C</t>
+          <t>MTP-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MP-08C</t>
+          <t>MTP-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1857,22 +1857,22 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>MTP-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>ASUB</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1881,22 +1881,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Housekeeping</t>
+          <t>Muestreo manual  de aguas subterráneas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>HOUSEKEEPING</t>
+          <t>MTP-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>ASUB</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Housekeeping</t>
+          <t>Muestreo manual  de aguas subterráneas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1905,46 +1905,46 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PTAS Puerto Collahuasi</t>
+          <t>MTP-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ASUB</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>S</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Muestreo Aguas Servidas</t>
+          <t>Muestreo manual  de aguas subterráneas</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PTAS Puerto Collahuasi</t>
+          <t>MTP-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>ASUB</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Muestreo Aguas Servidas</t>
+          <t>Muestreo manual  de aguas subterráneas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1953,22 +1953,22 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PEV-01 (PES-01)</t>
+          <t>HOUSEKEEPING</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ASUP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1977,22 +1977,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Muestreo manual de agua superficial</t>
+          <t>Housekeeping</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PEV-01 (PES-01)</t>
+          <t>HOUSEKEEPING</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ASUP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Muestreo manual de agua superficial</t>
+          <t>Housekeeping</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2001,775 +2001,7 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>ASUP</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Muestreo manual de agua superficial</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ASUP</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Muestreo manual de agua superficial</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J34" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>CGP</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Monitoreo en baños y casinos</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>CGP</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Monitoreo en baños y casinos</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J35" t="n">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>CGP</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ASUP</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Muestreo manual de agua superficial (agua potable)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>CGP</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ASUP</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Muestreo manual de agua superficial (agua potable)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
         <v>42</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>CPPCHE</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Monitoreo en baños y casinos</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>CPPCHE</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Monitoreo en baños y casinos</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>CPPCHE</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>ASUP</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Muestreo manual de agua superficial (agua potable)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>CPPCHE</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>ASUP</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Muestreo manual de agua superficial (agua potable)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>SALA DE CAMBIOS</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Monitoreo en salas de estación y TK</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>SALA DE CAMBIOS</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Monitoreo en salas de estación y TK</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>SALA DE CAMBIOS</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ASUP</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Muestreo manual de agua superficial (agua potable)</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>SALA DE CAMBIOS</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ASUP</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Muestreo manual de agua superficial (agua potable)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>TK-002</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Monitoreo en salas de estación y TK</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>TK-002</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>AP</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Monitoreo en salas de estación y TK</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>TK-002</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>ASUP</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Muestreo manual de agua superficial (agua potable)</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>TK-002</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ASUP</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Muestreo manual de agua superficial (agua potable)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>SH-02B</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>SH-02B</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J43" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>SH-06</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>SH-06</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J44" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>SH-07</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>1</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>SH-07</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>SH-08</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>SH-08</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>SH-19</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>SH-19</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Zanja Norte 1</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Zanja Norte 1</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Zanja Norte 2</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Zanja Norte 2</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>NF</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Medición de niveles freáticos</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/output/_temp/etapa_2_actualizacion_mensual/_interno/registros_turno_aplicado.xlsx
+++ b/output/_temp/etapa_2_actualizacion_mensual/_interno/registros_turno_aplicado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -519,7 +519,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BCON</t>
+          <t>BCC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,7 +528,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -542,7 +542,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BCON</t>
+          <t>BCC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -561,13 +561,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BGSO</t>
+          <t>BCON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BGSO</t>
+          <t>BCON</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BOR</t>
+          <t>BCON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>BOR</t>
+          <t>BCON</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BPCR</t>
+          <t>BGSO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BPCR</t>
+          <t>BGSO</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -705,13 +705,13 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C-1000</t>
+          <t>BGSO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C-1000</t>
+          <t>BGSO</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C-460</t>
+          <t>BOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C-460</t>
+          <t>BOR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CCD</t>
+          <t>BOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CCD</t>
+          <t>BOR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>BPCR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CPC</t>
+          <t>BPCR</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TK-1004</t>
+          <t>BPCR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -921,12 +921,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Monitoreo en salas de estación y TK</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TK-1004</t>
+          <t>BPCR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Monitoreo en salas de estación y TK</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -945,13 +945,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TK-505</t>
+          <t>C-1000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -969,12 +969,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monitoreo en salas de estación y TK</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TK-505</t>
+          <t>C-1000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Monitoreo en salas de estación y TK</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TK-517</t>
+          <t>C-1000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Monitoreo en salas de estación y TK</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>TK-517</t>
+          <t>C-1000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Monitoreo en salas de estación y TK</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1041,22 +1041,22 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MP-01A</t>
+          <t>C-460</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1065,22 +1065,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MP-01A</t>
+          <t>C-460</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1089,22 +1089,22 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MP-01B</t>
+          <t>C-460</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1113,22 +1113,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MP-01B</t>
+          <t>C-460</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1137,22 +1137,22 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MP-01B</t>
+          <t>CCD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1161,22 +1161,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MP-01B</t>
+          <t>CCD</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MP-01C</t>
+          <t>CCD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1209,22 +1209,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MP-01C</t>
+          <t>CCD</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1233,22 +1233,22 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MP-01C</t>
+          <t>CPC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1257,22 +1257,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MP-01C</t>
+          <t>CPC</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1281,22 +1281,22 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MP-02A</t>
+          <t>CPC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1305,22 +1305,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MP-02A</t>
+          <t>CPC</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en baños y casinos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1329,22 +1329,22 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MP-02A</t>
+          <t>TK-1004</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1353,22 +1353,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MP-02A</t>
+          <t>TK-1004</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1377,22 +1377,22 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MP-02B</t>
+          <t>TK-1004</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1401,22 +1401,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>MP-02B</t>
+          <t>TK-1004</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1425,22 +1425,22 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MP-02B</t>
+          <t>TK-505</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MP-02B</t>
+          <t>TK-505</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MP-02C</t>
+          <t>TK-505</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1497,22 +1497,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MP-02C</t>
+          <t>TK-505</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1521,22 +1521,22 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MP-02C</t>
+          <t>TK-517</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1545,22 +1545,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MP-02C</t>
+          <t>TK-517</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1569,22 +1569,22 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MP-03A</t>
+          <t>TK-517</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1593,22 +1593,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MP-03A</t>
+          <t>TK-517</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Monitoreo en salas de estación y TK</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1617,22 +1617,22 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MP-03A</t>
+          <t>CSW-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>CAUDAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1641,22 +1641,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Medición de caudal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>MP-03A</t>
+          <t>CSW-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>CAUDAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Medición de caudal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1665,22 +1665,22 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MP-03B</t>
+          <t>QDH-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>CAUDAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1689,22 +1689,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Medición de caudal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MP-03B</t>
+          <t>QDH-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>CAUDAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Medición de caudal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1713,22 +1713,22 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MP-03B</t>
+          <t>RF-2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1737,22 +1737,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Medición de niveles freáticos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>MP-03B</t>
+          <t>RF-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Medición de niveles freáticos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1761,22 +1761,22 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MP-03C</t>
+          <t>QSN-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>CAUDAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1785,22 +1785,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Medición de caudal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MP-03C</t>
+          <t>QSN-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>NF</t>
+          <t>CAUDAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Medición de niveles freáticos</t>
+          <t>Medición de caudal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1809,13 +1809,13 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MTP-09</t>
+          <t>RF-2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MTP-09</t>
+          <t>RF-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1857,22 +1857,22 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MTP-14</t>
+          <t>JCC-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>ASUP</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1881,22 +1881,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Muestreo manual de agua superficial</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MTP-14</t>
+          <t>JCC-04</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>ASUP</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Muestreo manual de agua superficial</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1905,46 +1905,46 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MTP-17</t>
+          <t>PUNTERA 2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Medición de niveles freáticos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MTP-17</t>
+          <t>PUNTERA 2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ASUB</t>
+          <t>NF</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Muestreo manual  de aguas subterráneas</t>
+          <t>Medición de niveles freáticos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1953,55 +1953,1687 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>JCC-05</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>15</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>JCC-05</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PUNTERA 2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>14</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PUNTERA 2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PLIX-04</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>15</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PLIX-04</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AFO-SA1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CAUDAL</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>14</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Medición de caudal</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AFO-SA1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>CAUDAL</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Medición de caudal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PLIX-04</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>15</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PLIX-04</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AFO-SA1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>14</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>AFO-SA1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>HOUSEKEEPING</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="C39" t="n">
+        <v>15</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
         <is>
           <t>Housekeeping</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>HOUSEKEEPING</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>HK</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Housekeeping</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Control SGS</t>
-        </is>
-      </c>
-      <c r="J33" t="n">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Estación 1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CAUDAL</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>14</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Medición de caudal</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Estación 1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CAUDAL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Medición de caudal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CGP</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>15</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Monitoreo en baños y casinos</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>CGP</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Monitoreo en baños y casinos</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Estación 1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>14</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Estación 1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CGP</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>15</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial (agua potable)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CGP</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial (agua potable)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dique Huinquintipa</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>14</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Dique Huinquintipa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CPPCHE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>15</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Monitoreo en baños y casinos</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CPPCHE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Monitoreo en baños y casinos</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Dique San Daniel</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>14</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Dique San Daniel</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>CPPCHE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>15</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial (agua potable)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CPPCHE</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial (agua potable)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>HOUSEKEEPING</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>14</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Housekeeping</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>HOUSEKEEPING</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Housekeeping</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SALA DE CAMBIOS</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>15</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Monitoreo en salas de estación y TK</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SALA DE CAMBIOS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Monitoreo en salas de estación y TK</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SALA DE CAMBIOS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial (agua potable)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SALA DE CAMBIOS</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial (agua potable)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TK-002</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>15</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Monitoreo en salas de estación y TK</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>TK-002</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Monitoreo en salas de estación y TK</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TK-002</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>15</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial (agua potable)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>TK-002</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ASUP</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Muestreo manual de agua superficial (agua potable)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PTAS Puerto Collahuasi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>15</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Muestreo Aguas Servidas</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>PTAS Puerto Collahuasi</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Muestreo Aguas Servidas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SH-02B</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>15</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>SH-02B</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SH-06</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>15</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SH-06</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SH-07</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>15</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>SH-07</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SH-08</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>15</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SH-08</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SH-19</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>15</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>SH-19</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SH-19</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>15</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>SH-19</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SH-20</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>15</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>SH-20</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SH-20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>15</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>SH-20</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SH-22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>15</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>SH-22</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
         <v>42</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SH-22</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>15</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>SH-22</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SH-23</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>15</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SH-23</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SH-23</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>15</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>SH-23</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>ASUB</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Muestreo manual  de aguas subterráneas</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Zanja Norte 1</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>15</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Zanja Norte 1</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Zanja Norte 2</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>15</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Zanja Norte 2</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>NF</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Medición de niveles freáticos</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Control SGS</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
